--- a/AutoMobChart1.0/truedata/indiv_schedules/CONIENDO, ROLAND CLINT JANDOG_Schedule.xlsx
+++ b/AutoMobChart1.0/truedata/indiv_schedules/CONIENDO, ROLAND CLINT JANDOG_Schedule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,37 +514,37 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -556,37 +556,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -598,37 +598,37 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -640,37 +640,37 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -682,37 +682,37 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -724,37 +724,37 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -766,37 +766,37 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -808,37 +808,37 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -850,37 +850,37 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -892,37 +892,37 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1438,37 +1438,37 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1480,37 +1480,37 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1522,37 +1522,37 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1564,37 +1564,37 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1606,37 +1606,37 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1648,37 +1648,37 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1690,17 +1690,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1732,17 +1732,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1774,17 +1774,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1900,17 +1900,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2194,17 +2194,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2236,17 +2236,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2298,17 +2298,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2320,17 +2320,17 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2362,17 +2362,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2424,17 +2424,17 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2446,37 +2446,37 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2488,37 +2488,37 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2530,37 +2530,37 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2572,37 +2572,37 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2614,37 +2614,37 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2656,37 +2656,37 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2698,37 +2698,37 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2740,37 +2740,37 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2782,37 +2782,37 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2824,37 +2824,37 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2866,37 +2866,37 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2908,37 +2908,37 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2950,37 +2950,37 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2992,37 +2992,37 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3034,37 +3034,37 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3076,37 +3076,37 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -3160,37 +3160,37 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
